--- a/PD_qc_report.xlsx
+++ b/PD_qc_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danielcm/Desktop/MIGUT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C3AD48-4B26-4C45-9734-5A9EF304AF5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F74CBE-3534-C745-ACAB-DA105C3A2AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4860" yWindow="1600" windowWidth="29020" windowHeight="18800" xr2:uid="{594BDCD8-4B93-0B4B-A293-6C1C2C6C6272}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="384">
   <si>
     <t>Top overrepresented sequences</t>
   </si>
@@ -1191,9 +1191,6 @@
   </si>
   <si>
     <t>N/A</t>
-  </si>
-  <si>
-    <t>Prinseq derep -124 (removes exact duplicates, 5' duplicates, and 3' duplicates)</t>
   </si>
 </sst>
 </file>
@@ -2037,7 +2034,7 @@
       <c r="T1" s="15"/>
       <c r="U1" s="16"/>
       <c r="V1" s="18" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="W1" s="18"/>
       <c r="X1" s="18"/>
